--- a/themes/loansConsultation.xlsx
+++ b/themes/loansConsultation.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -450,154 +450,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Ознакомиться с имеющимися кредитными продуктами и условиями их оформления вы можете по [ссылке]({{$temp.LoanLink}})</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Ознакомиться с имеющимися кредитными продуктами и условиями их оформления вы можете по [ссылке]({{$temp.LoanLink}}).</t>
+          <t xml:space="preserve">    Заявка, поданная за час до закрытия или во время закрытия операционного дня — аннулируется.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>сомнительное место: тире перед глаголом «аннулируется» («... операционного дня — аннулируется») нестандартно для правила тире между подлежащим и сказуемым. Возможно, авторское тире для акцента — не стал убирать сам</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60</v>
+        <v>162</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - "Посмотреть подробности можете в [личном кабинете]({{$temp.loan.DBOLoanDetailsLink}})"</t>
+          <t xml:space="preserve">    - Для того, чтобы я могу проинформировать вас по вопросам ПТС, укажите город, в котором вы оформляли автокредит.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - "Посмотреть подробности можете в [личном кабинете]({{$temp.loan.DBOLoanDetailsLink}})."</t>
+          <t xml:space="preserve">    - Для того, чтобы я мог проинформировать вас по вопросам ПТС, укажите город, в котором вы оформляли автокредит.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>«могу» исправлено на «мог» — после союза «чтобы» требуется форма прошедшего времени (сослагательное наклонение)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      - "Подать заявление на досрочное погашение кредитного договора №{{ $session.loan.num }} вы можете по [ссылке]({{$temp.LoanPartRepaymentLink}})"</t>
+          <t xml:space="preserve">     Если вы оставляли ПТС в автосалоне, то необходимо обратиться в отделение по адресу: г. Уфа ул. Крупской 9.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      - "Подать заявление на досрочное погашение кредитного договора №{{ $session.loan.num }} вы можете по [ссылке]({{$temp.LoanPartRepaymentLink}})."</t>
+          <t xml:space="preserve">     Если вы оставляли ПТС в автосалоне, то необходимо обратиться в отделение по адресу: г. Уфа, ул. Крупской, 9.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>98</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - "Подать заявление на полное досрочное погашение кредитного договора №{{ $session.loan.num }} можно по [ссылке]({{$temp.LoanFullRepaymentLink}})"</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - "Подать заявление на полное досрочное погашение кредитного договора №{{ $session.loan.num }} можно по [ссылке]({{$temp.LoanFullRepaymentLink}})."</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>105</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Заявка, поданная за час до закрытия или во время закрытия операционного дня — аннулируется.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>сомнительное место: тире перед глаголом «аннулируется» («... операционного дня — аннулируется») нестандартно для правила тире между подлежащим и сказуемым. Возможно, авторское тире для акцента — не стал убирать сам</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>131</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Список отделений доступен по [ссылке]({{ $temp.officeLink }})</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Список отделений доступен по [ссылке]({{ $temp.officeLink }}).</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>162</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - Для того, чтобы я могу проинформировать вас по вопросам ПТС, укажите город, в котором вы оформляли автокредит.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - Для того, чтобы я мог проинформировать вас по вопросам ПТС, укажите город, в котором вы оформляли автокредит.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>«могу» исправлено на «мог» — после союза «чтобы» требуется форма прошедшего времени (сослагательное наклонение)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>171</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Если вы оставляли ПТС в автосалоне, то необходимо обратиться в отделение по адресу: г. Уфа ул. Крупской 9.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Если вы оставляли ПТС в автосалоне, то необходимо обратиться в отделение по адресу: г. Уфа, ул. Крупской, 9.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
         <is>
           <t>добавлены запятые между элементами адреса</t>
         </is>
